--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/26 17:20:36</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>31666</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>266000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>266000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31666.67</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>31666</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>31666.67</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/26 15:30:53</t>
+          <t>08/27 16:33:14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>140000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>16666.67</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/26 17:20:36</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>31666</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>140000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>266000</t>
+          <t>16666.67</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>31666.67</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>31666</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.67</t>
+          <t>16666.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/27 18:05:14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16666</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>140000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>140000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16666.67</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16666</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>16666.67</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.67</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/27 16:33:14</t>
+          <t>08/28 11:17:30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>5952.38</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/27 18:05:14</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16666</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>140000</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16666.67</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16666</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.67</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/28 11:17:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5952.38</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5564.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>08/28 14:02:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5564</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>08/28 11:17:38</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>388</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>5952.38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5952</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5564.38</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.38</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/28 11:17:30</t>
+          <t>08/30 10:19:15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,12 +95,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5952.38</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t/>
+          <t>胡琪斌</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/28 14:02:52</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5564</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08/28 11:17:38</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5952.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5952</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.38</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08/30 12:44:48</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08/30 10:19:15</t>
+          <t>09/02 15:56:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>9036.14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>胡琪斌</t>
+          <t>许定勇</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>08/30 12:44:48</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11904</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>75000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>9036.14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11904</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.76</t>
+          <t>9036.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/02 16:53:50</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>75000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>75000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9036.14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>9036.14</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8036.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>09/02 17:19:29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8036</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>09/02 16:53:50</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>75000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>75000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>9036.14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>9036</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8036.14</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.14</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/02 15:56:24</t>
+          <t>09/03 12:12:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9036.14</t>
+          <t>11309.52</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>许定勇</t>
+          <t>毕春丽</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/02 17:19:29</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8036</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/02 16:53:50</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>95000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>11309.52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>75000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>9036.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>9036</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.14</t>
+          <t>11309.52</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>09/03 14:05:04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11627.91</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>贾凌</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>09/03 12:12:00</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>95000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>11309.52</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>毕春丽</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>95000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11309.52</t>
+          <t>195000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22937.43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11309.52</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22937.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>09/03 14:06:24</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>195000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22937.43</t>
+          <t>195000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22937.43</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22937.43</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21937.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>09/03 15:50:47</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21937</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>09/03 14:06:24</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>jxxiaomei521</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>195000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22937.43</t>
+          <t>195000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>22937.43</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22937</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>21937.43</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.43</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/03 14:05:04</t>
+          <t>09/04 17:04:18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>70000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,22 +90,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11627.91</t>
+          <t>8536.59</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>贾凌</t>
+          <t>唐志刚</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -114,240 +114,144 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>09/03 12:12:00</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>95000</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>8.4</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>11309.52</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>毕春丽</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>09/03 15:50:47</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>21937</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>09/03 14:06:24</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
+          <t>70000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8536.59</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>195000</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>应下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22937.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>22937</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.43</t>
+          <t>8536.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/04 18:27:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>8536</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>70000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8536.59</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8536</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>8536.59</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.59</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/04 17:04:18</t>
+          <t>09/05 16:45:49</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>50000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>6097.56</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/04 18:27:05</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>8536</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>70000</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>8536.59</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8536</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.59</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/05 18:36:53</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>50000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>50000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6097.56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6097</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>6097.56</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.56</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09/05 16:45:49</t>
+          <t>09/08 12:06:24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>11904.76</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>唐志刚</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09/05 18:36:53</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>6097</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6097.56</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6097</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.56</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
+++ b/bills/JXZFSP01/-5580359657/b1373c381a1a1dd70c70533b5d4c97626ced8f296f0ca54b71ec975f62a00938/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>09/08 15:08:10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11904.76</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11904.76</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11904</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11904.76</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.76</t>
         </is>
       </c>
     </row>
